--- a/Data/IP_FnResp_ofTheUnionandStates.xlsx
+++ b/Data/IP_FnResp_ofTheUnionandStates.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,401 +472,401 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
+          <t>Prisons come under which list?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It divides powers into Union, State, and Concurrent Lists.</t>
+          <t>Administration of jails is a State function.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which list contains subjects on which only the Union Government can legislate?</t>
+          <t>The Constitution provides for inter-governmental coordination through</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>District Magistrates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It includes defense, foreign affairs, etc.</t>
+          <t>They promote cooperation among states and Centre.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subjects like police, public health, and local government belong to which list?</t>
+          <t>Which body resolves disputes between Centre and States?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>These are under state jurisdiction.</t>
+          <t>As per Article 131.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Education falls under which list?</t>
+          <t>Which entry in the State List deals with public health and sanitation?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Entry 8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate on it.</t>
+          <t>Covers hospitals, sanitation, etc.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Residuary powers in India belong to</t>
+          <t>In Union-State relation, India follows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Dual Federalism</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Confederalism</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Unitary System</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>Centre and States work together.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
+          <t>Which of the following is a subject under the Union List?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Union law prevails in case of conflict.</t>
+          <t>Only the Union can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
+          <t>State governments derive power to legislate from</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Defines Union executive powers.</t>
+          <t>As per Article 246.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The power to legislate on a State List subject during an emergency lies with</t>
+          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>During national emergency, Parliament can legislate on State List.</t>
+          <t>Unless State law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Water supply, sanitation, and public health are responsibilities of</t>
+          <t>Inter-State Trade and Commerce is a subject under</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>They are listed in the State List.</t>
+          <t>Only Parliament can regulate it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Who governs the relation between Centre and States in financial matters?</t>
+          <t>Education falls under which list?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It recommends tax distribution.</t>
+          <t>Both Centre and State can legislate on it.</t>
         </is>
       </c>
     </row>
@@ -912,771 +912,767 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which body resolves disputes between Centre and States?</t>
+          <t>Land is a subject in</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>As per Article 131.</t>
+          <t>States legislate on land.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agriculture is listed under which list?</t>
+          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Entry 1A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Agriculture is a state subject.</t>
+          <t>It includes defense of India and armed forces.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which of the following is a subject under the Union List?</t>
+          <t>The idea of division of powers between Union and States is based on</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>UK Constitution</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>USA Constitution</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>French Constitution</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Only the Union can legislate on it.</t>
+          <t>India follows a stronger Centre model.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Concurrent List is also known as</t>
+          <t>Which is true about Union List?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State-exclusive list</t>
+          <t>States can legislate</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union-exclusive list</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>States and Centre legislate together</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Because both Union and State can legislate.</t>
+          <t>States have no authority.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Forests and wild animal protection fall under</t>
+          <t>Education was transferred to the Concurrent List by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>86th Amendment</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Both Centre and State can make laws.</t>
+          <t>To ensure uniform education policy.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
+          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>State prevails</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Both are invalid</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Supreme Court decides</t>
+          <t>State Assembly</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>As per Article 254.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How many subjects are currently there in the State List?</t>
+          <t>During President’s Rule, State List powers are exercised by</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>State Governor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>After the 42nd Amendment.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The State Government gets revenue from</t>
+          <t>Article 262 deals with disputes relating to</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Customs</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Forests</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Corporation Tax</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>State subjects include land and property taxes.</t>
+          <t>It provides for adjudication of inter-State water disputes.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who prepares the Union Budget?</t>
+          <t>Union Government can legislate on State List during</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Normal time</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Governor’s consent</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Presented in Parliament.</t>
+          <t>Article 250 enables this.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Constitution provides for inter-governmental coordination through</t>
+          <t>Who governs the relation between Centre and States in financial matters?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Finance Commission</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Planning Commission</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NITI Aayog</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Governor</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zonal Councils</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>District Magistrates</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CAG</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>They promote cooperation among states and Centre.</t>
+          <t>It recommends tax distribution.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
+          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>These are residuary powers.</t>
+          <t>Defines Union executive powers.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Language policy is a matter under</t>
+          <t>State List initially had how many entries?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate.</t>
+          <t>Some moved to Concurrent List later.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The power to reorganize the states in India lies with</t>
+          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Article 254</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Under Article 3.</t>
+          <t>Specifies territorial limits of legislative powers.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which commission reviews Centre-State relations in India?</t>
+          <t>Subjects like police, public health, and local government belong to which list?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Administrative Reforms Commission</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Established under Article 263.</t>
+          <t>These are under state jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
+          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 254</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Specifies territorial limits of legislative powers.</t>
+          <t>These are residuary powers.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Union can legislate on a State subject if</t>
+          <t>Concurrent List initially had how many entries?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>President gives consent</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Supreme Court orders</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prime Minister directs</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>Now increased slightly.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
+          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6th Schedule</t>
+          <t>State law prevails</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Both become void</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>9th Schedule</t>
-        </is>
-      </c>
+          <t>Centre law prevails</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Centre law prevails</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It contains Union, State, and Concurrent Lists.</t>
+          <t>Unless state law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
+          <t>Which of these is a State subject?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Atomic Energy</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent Lists.</t>
+          <t>Only States can legislate on agriculture.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The subject of 'banking' falls under which list?</t>
+          <t>If a subject is not in any list, who can make law on it?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on it.</t>
+          <t>Residuary power lies with Parliament.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Labour laws are included in which list?</t>
+          <t>Public Health is listed under</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1686,14 +1682,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Residuary List</t>
@@ -1701,302 +1697,302 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Both Union and State can legislate.</t>
+          <t>States are primarily responsible.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which body recommends how taxes are distributed between Centre and States?</t>
+          <t>The power to legislate on a State List subject during an emergency lies with</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Constituted every 5 years under Article 280.</t>
+          <t>During national emergency, Parliament can legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Law and order is primarily a responsibility of</t>
+          <t>The concept of three lists in Indian Constitution was borrowed from</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>7th Schedule follows Australian model.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Article deals with the relationship between Union and State executive powers?</t>
+          <t>Which entry relates to defense in Union List?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Entry 3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Entry 5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>It defines executive power of the Union.</t>
+          <t>It includes armed forces.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The term "Federal" is used in the Indian Constitution in</t>
+          <t>Which of the following is *not* a State subject?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Preamble</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>India is a quasi-federal state, but the term isn't directly used.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
+          <t>Residuary powers in India belong to</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Law and order</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Allows both Centre and State to make laws on it.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The residuary powers in the USA are vested in</t>
+          <t>The Constitution distributes legislative powers between Centre and States in</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Federal Government</t>
+          <t>Two lists</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Four lists</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>No list</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Unlike India, where they are with Centre.</t>
+          <t>Union, State, and Concurrent lists.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a State subject?</t>
+          <t>Who decides whether a matter is a residuary subject?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>It interprets Constitution.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Planning and Economic Development fall under</t>
+          <t>Labour laws are included in which list?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2006,17 +2002,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>State List</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>State List</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2026,127 +2022,127 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Both levels can plan for development.</t>
+          <t>Both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>During President’s Rule, State List powers are exercised by</t>
+          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>State Governor</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>Subjects like forests, education were shifted.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Union Government can legislate on State List during</t>
+          <t>Entry related to education in the Concurrent List is</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Normal time</t>
+          <t>Entry 11A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Entry 42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Governor’s consent</t>
+          <t>Entry 29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Article 250 enables this.</t>
+          <t>Post-42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
+          <t>Agriculture is under which list?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Subjects like forests, education were shifted.</t>
+          <t>States have exclusive power on this.</t>
         </is>
       </c>
     </row>
@@ -2192,371 +2188,371 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concurrent List was borrowed from the Constitution of</t>
+          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>India’s federal model draws from several countries.</t>
+          <t>It divides powers into Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Public health is a subject in which list?</t>
+          <t>Which body recommends how taxes are distributed between Centre and States?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>States are responsible for hospitals and sanitation.</t>
+          <t>Constituted every 5 years under Article 280.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Disputes between States are decided by</t>
+          <t>What does Article 246 deal with?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Dispute Redressal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Financial emergency</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Emergency Provisions</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Under Article 131.</t>
+          <t>Among Union and State.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A State law on a Concurrent subject must get President’s assent if</t>
+          <t>Who has exclusive power to make laws on residuary subjects?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>State Legislatures</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>It is passed unanimously</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>It has national scope</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Otherwise Union law will prevail.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Article 262 deals with disputes relating to</t>
+          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Forests</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>It provides for adjudication of inter-State water disputes.</t>
+          <t>Can be renewed.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The idea of division of powers between Union and States is based on</t>
+          <t>Concurrent List was borrowed from the Constitution of</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UK Constitution</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>USA Constitution</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>French Constitution</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>India follows a stronger Centre model.</t>
+          <t>India’s federal model draws from several countries.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a Concurrent List subject?</t>
+          <t>Which of the following comes under Union List?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marriage and Divorce</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Criminal Procedure</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>It is a Union List subject.</t>
+          <t>States cannot legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
+          <t>The term "Federal" is used in the Indian Constitution in</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Preamble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Entry 10</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Entry 1A</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>It includes defense of India and armed forces.</t>
+          <t>India is a quasi-federal state, but the term isn't directly used.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The power to legislate on residuary subjects lies with</t>
+          <t>Planning is a subject under</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Both Centre and States</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>As per Article 248.</t>
+          <t>Both Centre and States can plan.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inter-State Trade and Commerce is a subject under</t>
+          <t>Language policy is a matter under</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2566,922 +2562,922 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>None of these</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Residuary List</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Union List</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Only Parliament can regulate it.</t>
+          <t>Both Centre and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
+          <t>Electricity appears in which list of the Constitution?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Part XII</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Covers Articles 245 to 255.</t>
+          <t>Both can legislate.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Union can legislate on matters in the State List during</t>
+          <t>Which list contains matters like adoption, succession, and divorce?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Normal times</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Constitutional Emergency</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Under Article 250.</t>
+          <t>Both Parliament and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Police and Public Order are primarily under</t>
+          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>6th Schedule</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>These are State subjects.</t>
+          <t>It contains Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
+          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Yes, if President allows</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No need for State consent.</t>
+          <t>Article 250 allows this.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
+          <t>Disputes between States are decided by</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Unless State law has President’s assent.</t>
+          <t>Under Article 131.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which entry in the State List deals with public health and sanitation?</t>
+          <t>The power to reorganize the states in India lies with</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Entry 7</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Entry 9</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Entry 8</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Covers hospitals, sanitation, etc.</t>
+          <t>Under Article 3.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agriculture is under which list?</t>
+          <t>Union-State relations are mentioned in which part?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Part XIII</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>States have exclusive power on this.</t>
+          <t>Covers legislative, administrative and financial relations.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Electricity appears in which list of the Constitution?</t>
+          <t>The Union can legislate on a State subject if</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>President gives consent</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court orders</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Prime Minister directs</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Both can legislate.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The concept of three lists in Indian Constitution was borrowed from</t>
+          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7th Schedule follows Australian model.</t>
+          <t>Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Union List has how many subjects?</t>
+          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Originally had 97 entries.</t>
+          <t>Union law prevails in case of conflict.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>State List initially had how many entries?</t>
+          <t>The Union can legislate on matters in the State List during</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Normal times</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Financial Emergency</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>Constitutional Emergency</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Some moved to Concurrent List later.</t>
+          <t>Under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concurrent List initially had how many entries?</t>
+          <t>Law and order is primarily a responsibility of</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Now increased slightly.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Forests were moved from State to Concurrent List by</t>
+          <t>The State Government gets revenue from</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Customs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>101st Amendment</t>
+          <t>Corporation Tax</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>To ensure national policy.</t>
+          <t>State subjects include land and property taxes.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>In Union-State relation, India follows</t>
+          <t>Police and Public Order are primarily under</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dual Federalism</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Confederalism</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Unitary System</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Centre and States work together.</t>
+          <t>These are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mines and minerals fall under which list?</t>
+          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>But regulation is also under Union in some cases.</t>
+          <t>Advises on coordination and disputes.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Waterfalls under which subject in Indian Constitution?</t>
+          <t>Which commission reviews Centre-State relations in India?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Administrative Reforms Commission</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Not Mentioned</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Irrigation, water supply are State subjects.</t>
+          <t>Established under Article 263.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Entry related to education in the Concurrent List is</t>
+          <t>Which list contains subjects on which only the Union Government can legislate?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Entry 11A</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Entry 42</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Entry 29</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Post-42nd Amendment.</t>
+          <t>It includes defense, foreign affairs, etc.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
+          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yes, if President allows</t>
+          <t>Law and order</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Article 250 allows this.</t>
+          <t>Allows both Centre and State to make laws on it.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of the following comes under Union List?</t>
+          <t>Which subject is included in the Union List?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Trade unions</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Prisons</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Public Health</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>States cannot legislate on it.</t>
+          <t>Only Parliament can legislate on banking.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Prisons come under which list?</t>
+          <t>Centre can make laws on State List during</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Normal Times</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Only with SC permission</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>When State consents</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Administration of jails is a State function.</t>
+          <t>As per Article 250.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
+          <t>The subject of 'banking' falls under which list?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Central Law</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Whichever is better</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>As per judicial interpretation.</t>
+          <t>Only Parliament can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
+          <t>The residuary powers in the USA are vested in</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Federal Government</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Advises on coordination and disputes.</t>
+          <t>Unlike India, where they are with Centre.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which subject is included in the Union List?</t>
+          <t>Which of the following is *not* a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Trade unions</t>
+          <t>Marriage and Divorce</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3491,12 +3487,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Criminal Procedure</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3506,127 +3502,127 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on banking.</t>
+          <t>It is a Union List subject.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Constitution distributes legislative powers between Centre and States in</t>
+          <t>A State law on a Concurrent subject must get President’s assent if</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Two lists</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>It is passed unanimously</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Four lists</t>
+          <t>It has national scope</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>No list</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent lists.</t>
+          <t>Otherwise Union law will prevail.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Education was transferred to the Concurrent List by</t>
+          <t>Agriculture is listed under which list?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>86th Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>To ensure uniform education policy.</t>
+          <t>Agriculture is a state subject.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Concurrent List is found in</t>
+          <t>Mines and minerals fall under which list?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Schedule 6</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Schedule 8</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Schedule 9</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It contains subjects both Centre and States legislate on.</t>
+          <t>But regulation is also under Union in some cases.</t>
         </is>
       </c>
     </row>
@@ -3672,171 +3668,171 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which list contains matters like adoption, succession, and divorce?</t>
+          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Central Law</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Whichever is better</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Both Parliament and State can legislate.</t>
+          <t>As per judicial interpretation.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>State governments derive power to legislate from</t>
+          <t>Concurrent List is also known as</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State-exclusive list</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Union-exclusive list</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>As per Article 246.</t>
+          <t>Because both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Public Health is listed under</t>
+          <t>Waterfalls under which subject in Indian Constitution?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>State List</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Union List</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Not Mentioned</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Residuary List</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>State List</t>
-        </is>
-      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>States are primarily responsible.</t>
+          <t>Irrigation, water supply are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which subject is not included in the State List?</t>
+          <t>Which is not a function of the Union Government?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Police</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Communications</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Local Government</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Planning is a subject under</t>
+          <t>Planning and Economic Development fall under</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3846,157 +3842,157 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>None of these</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Not mentioned</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Both Centre and States can plan.</t>
+          <t>Both levels can plan for development.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
+          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>State prevails</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Both are invalid</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>State Assembly</t>
+          <t>Supreme Court decides</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>As per Article 254.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which is true about Union List?</t>
+          <t>Which subject is not included in the State List?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>States can legislate</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>States and Centre legislate together</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Local Government</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>States have no authority.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What does Article 246 deal with?</t>
+          <t>Concurrent List allows</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dispute Redressal</t>
+          <t>Only Centre to legislate</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Financial emergency</t>
+          <t>Only States to legislate</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emergency Provisions</t>
+          <t>Neither</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Among Union and State.</t>
+          <t>But Centre law prevails on conflict.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Land is a subject in</t>
+          <t>Public health is a subject in which list?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4016,7 +4012,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4026,22 +4022,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>States legislate on land.</t>
+          <t>States are responsible for hospitals and sanitation.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Who has exclusive power to make laws on residuary subjects?</t>
+          <t>The power to legislate on residuary subjects lies with</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>State Legislatures</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4051,422 +4047,422 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Both Centre and States</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>As per Article 248.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
+          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>State law prevails</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Both become void</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Part XII</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Unless state law has President’s assent.</t>
+          <t>Covers Articles 245 to 255.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Union-State relations are mentioned in which part?</t>
+          <t>Union List has how many subjects?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Part XIII</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Covers legislative, administrative and financial relations.</t>
+          <t>Originally had 97 entries.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of these is a State subject?</t>
+          <t>Which Article deals with the relationship between Union and State executive powers?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atomic Energy</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Only States can legislate on agriculture.</t>
+          <t>It defines executive power of the Union.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who decides whether a matter is a residuary subject?</t>
+          <t>Water supply, sanitation, and public health are responsibilities of</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>State Government</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>It interprets Constitution.</t>
+          <t>They are listed in the State List.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Centre can make laws on State List during</t>
+          <t>Forests were moved from State to Concurrent List by</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Normal Times</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Only with SC permission</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>When State consents</t>
+          <t>101st Amendment</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>As per Article 250.</t>
+          <t>To ensure national policy.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
+          <t>How many subjects are currently there in the State List?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Can be renewed.</t>
+          <t>After the 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is not a function of the Union Government?</t>
+          <t>The Concurrent List is found in</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Schedule 6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Foreign Affairs</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Schedule 8</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Schedule 9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>It contains subjects both Centre and States legislate on.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which entry relates to defense in Union List?</t>
+          <t>Who prepares the Union Budget?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Entry 3</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Entry 5</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>It includes armed forces.</t>
+          <t>Presented in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Concurrent List allows</t>
+          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Only Centre to legislate</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Only States to legislate</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Neither</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>But Centre law prevails on conflict.</t>
+          <t>No need for State consent.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>If a subject is not in any list, who can make law on it?</t>
+          <t>Forests and wild animal protection fall under</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Residuary power lies with Parliament.</t>
+          <t>Both Centre and State can make laws.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_FnResp_ofTheUnionandStates.xlsx
+++ b/Data/IP_FnResp_ofTheUnionandStates.xlsx
@@ -472,11 +472,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prisons come under which list?</t>
+          <t>Forests and wild animal protection fall under</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,14 +486,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>State List</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>State List</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Residuary List</t>
@@ -501,422 +501,422 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Administration of jails is a State function.</t>
+          <t>Both Centre and State can make laws.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Constitution provides for inter-governmental coordination through</t>
+          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>District Magistrates</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>They promote cooperation among states and Centre.</t>
+          <t>No need for State consent.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which body resolves disputes between Centre and States?</t>
+          <t>Who prepares the Union Budget?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>As per Article 131.</t>
+          <t>Presented in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which entry in the State List deals with public health and sanitation?</t>
+          <t>The Concurrent List is found in</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Schedule 6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Entry 7</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Entry 9</t>
+          <t>Schedule 8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entry 8</t>
+          <t>Schedule 9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Covers hospitals, sanitation, etc.</t>
+          <t>It contains subjects both Centre and States legislate on.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In Union-State relation, India follows</t>
+          <t>How many subjects are currently there in the State List?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dual Federalism</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Confederalism</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Unitary System</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Centre and States work together.</t>
+          <t>After the 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which of the following is a subject under the Union List?</t>
+          <t>Forests were moved from State to Concurrent List by</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>101st Amendment</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Only the Union can legislate on it.</t>
+          <t>To ensure national policy.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>State governments derive power to legislate from</t>
+          <t>Water supply, sanitation, and public health are responsibilities of</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Union Government</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>State Government</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>State List in Schedule 7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Finance Commission</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>As per Article 246.</t>
+          <t>They are listed in the State List.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
+          <t>Which Article deals with the relationship between Union and State executive powers?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Unless State law has President’s assent.</t>
+          <t>It defines executive power of the Union.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inter-State Trade and Commerce is a subject under</t>
+          <t>Union List has how many subjects?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Only Parliament can regulate it.</t>
+          <t>Originally had 97 entries.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Education falls under which list?</t>
+          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Part XII</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate on it.</t>
+          <t>Covers Articles 245 to 255.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which list is also known as List I in the Seventh Schedule?</t>
+          <t>The power to legislate on residuary subjects lies with</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Both Centre and States</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>It contains 97 subjects.</t>
+          <t>As per Article 248.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Land is a subject in</t>
+          <t>Public health is a subject in which list?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -946,750 +946,754 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>States legislate on land.</t>
+          <t>States are responsible for hospitals and sanitation.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
+          <t>Concurrent List allows</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Only Centre to legislate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Entry 10</t>
+          <t>Only States to legislate</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Entry 1A</t>
+          <t>Neither</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It includes defense of India and armed forces.</t>
+          <t>But Centre law prevails on conflict.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The idea of division of powers between Union and States is based on</t>
+          <t>Which subject is not included in the State List?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UK Constitution</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USA Constitution</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>French Constitution</t>
+          <t>Local Government</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>India follows a stronger Centre model.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which is true about Union List?</t>
+          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>States can legislate</t>
+          <t>State prevails</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>States and Centre legislate together</t>
+          <t>Both are invalid</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Supreme Court decides</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>States have no authority.</t>
+          <t>As per Article 254.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Education was transferred to the Concurrent List by</t>
+          <t>Planning and Economic Development fall under</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>86th Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>To ensure uniform education policy.</t>
+          <t>Both levels can plan for development.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
+          <t>Which is not a function of the Union Government?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Foreign Affairs</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>State Assembly</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>During President’s Rule, State List powers are exercised by</t>
+          <t>Waterfalls under which subject in Indian Constitution?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>State Governor</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Not Mentioned</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>Irrigation, water supply are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Article 262 deals with disputes relating to</t>
+          <t>Concurrent List is also known as</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>State-exclusive list</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Union-exclusive list</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Forests</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>It provides for adjudication of inter-State water disputes.</t>
+          <t>Because both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Union Government can legislate on State List during</t>
+          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Normal time</t>
+          <t>Central Law</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Governor’s consent</t>
+          <t>Whichever is better</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Article 250 enables this.</t>
+          <t>As per judicial interpretation.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who governs the relation between Centre and States in financial matters?</t>
+          <t>During a President's Rule, Parliament can legislate on</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Union List only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>Concurrent List only</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Only with Governor's consent</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It recommends tax distribution.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
+          <t>Mines and minerals fall under which list?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Defines Union executive powers.</t>
+          <t>But regulation is also under Union in some cases.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State List initially had how many entries?</t>
+          <t>Agriculture is listed under which list?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Some moved to Concurrent List later.</t>
+          <t>Agriculture is a state subject.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
+          <t>A State law on a Concurrent subject must get President’s assent if</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>It is passed unanimously</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>It has national scope</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Article 254</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Specifies territorial limits of legislative powers.</t>
+          <t>Otherwise Union law will prevail.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subjects like police, public health, and local government belong to which list?</t>
+          <t>Which of the following is *not* a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Marriage and Divorce</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Criminal Procedure</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>These are under state jurisdiction.</t>
+          <t>It is a Union List subject.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
+          <t>The residuary powers in the USA are vested in</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Federal Government</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>These are residuary powers.</t>
+          <t>Unlike India, where they are with Centre.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Concurrent List initially had how many entries?</t>
+          <t>The subject of 'banking' falls under which list?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Now increased slightly.</t>
+          <t>Only Parliament can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
+          <t>Centre can make laws on State List during</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>State law prevails</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Both become void</t>
+          <t>Normal Times</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>Only with SC permission</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>When State consents</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Unless state law has President’s assent.</t>
+          <t>As per Article 250.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of these is a State subject?</t>
+          <t>Which subject is included in the Union List?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Trade unions</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atomic Energy</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Only States can legislate on agriculture.</t>
+          <t>Only Parliament can legislate on banking.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>If a subject is not in any list, who can make law on it?</t>
+          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Law and order</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Residuary power lies with Parliament.</t>
+          <t>Allows both Centre and State to make laws on it.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Public Health is listed under</t>
+          <t>Which list contains subjects on which only the Union Government can legislate?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>State List</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Union List</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>State List</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Residuary List</t>
@@ -1697,1559 +1701,1559 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>States are primarily responsible.</t>
+          <t>It includes defense, foreign affairs, etc.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The power to legislate on a State List subject during an emergency lies with</t>
+          <t>Which commission reviews Centre-State relations in India?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Administrative Reforms Commission</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>During national emergency, Parliament can legislate on State List.</t>
+          <t>Established under Article 263.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The concept of three lists in Indian Constitution was borrowed from</t>
+          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7th Schedule follows Australian model.</t>
+          <t>Advises on coordination and disputes.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which entry relates to defense in Union List?</t>
+          <t>Police and Public Order are primarily under</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Entry 3</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entry 5</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>It includes armed forces.</t>
+          <t>These are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a State subject?</t>
+          <t>The State Government gets revenue from</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Customs</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Corporation Tax</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>State subjects include land and property taxes.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Residuary powers in India belong to</t>
+          <t>Law and order is primarily a responsibility of</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Union Government</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>State Government</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Union Government</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Constitution distributes legislative powers between Centre and States in</t>
+          <t>The Union can legislate on matters in the State List during</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Two lists</t>
+          <t>Normal times</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>Financial Emergency</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Four lists</t>
+          <t>Constitutional Emergency</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>No list</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent lists.</t>
+          <t>Under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who decides whether a matter is a residuary subject?</t>
+          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Governor</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>It interprets Constitution.</t>
+          <t>Union law prevails in case of conflict.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Labour laws are included in which list?</t>
+          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Both Union and State can legislate.</t>
+          <t>Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
+          <t>The Union can legislate on a State subject if</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>President gives consent</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Supreme Court orders</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Prime Minister directs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Subjects like forests, education were shifted.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Entry related to education in the Concurrent List is</t>
+          <t>Union-State relations are mentioned in which part?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Entry 11A</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Entry 42</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Part XIII</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Entry 29</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Post-42nd Amendment.</t>
+          <t>Covers legislative, administrative and financial relations.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agriculture is under which list?</t>
+          <t>The power to reorganize the states in India lies with</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>States have exclusive power on this.</t>
+          <t>Under Article 3.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
+          <t>Disputes between States are decided by</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>By 2/3rd majority, under Article 249.</t>
+          <t>Under Article 131.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
+          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Yes, if President allows</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>It divides powers into Union, State, and Concurrent Lists.</t>
+          <t>Article 250 allows this.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which body recommends how taxes are distributed between Centre and States?</t>
+          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>6th Schedule</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Constituted every 5 years under Article 280.</t>
+          <t>It contains Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What does Article 246 deal with?</t>
+          <t>Which list contains matters like adoption, succession, and divorce?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dispute Redressal</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Financial emergency</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Emergency Provisions</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Among Union and State.</t>
+          <t>Both Parliament and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who has exclusive power to make laws on residuary subjects?</t>
+          <t>Electricity appears in which list of the Constitution?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Legislatures</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>Both can legislate.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
+          <t>Language policy is a matter under</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Can be renewed.</t>
+          <t>Both Centre and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concurrent List was borrowed from the Constitution of</t>
+          <t>Planning is a subject under</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>India’s federal model draws from several countries.</t>
+          <t>Both Centre and States can plan.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following comes under Union List?</t>
+          <t>The term "Federal" is used in the Indian Constitution in</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Preamble</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>States cannot legislate on it.</t>
+          <t>India is a quasi-federal state, but the term isn't directly used.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The term "Federal" is used in the Indian Constitution in</t>
+          <t>Which of the following comes under Union List?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Preamble</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>India is a quasi-federal state, but the term isn't directly used.</t>
+          <t>States cannot legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Planning is a subject under</t>
+          <t>Concurrent List was borrowed from the Constitution of</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Both Centre and States can plan.</t>
+          <t>India’s federal model draws from several countries.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Language policy is a matter under</t>
+          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate.</t>
+          <t>Can be renewed.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Electricity appears in which list of the Constitution?</t>
+          <t>Who has exclusive power to make laws on residuary subjects?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State Legislatures</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Both can legislate.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which list contains matters like adoption, succession, and divorce?</t>
+          <t>What does Article 246 deal with?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Dispute Redressal</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Financial emergency</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Emergency Provisions</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Both Parliament and State can legislate.</t>
+          <t>Among Union and State.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
+          <t>Which body recommends how taxes are distributed between Centre and States?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6th Schedule</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>It contains Union, State, and Concurrent Lists.</t>
+          <t>Constituted every 5 years under Article 280.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
+          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yes, if President allows</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Article 250 allows this.</t>
+          <t>It divides powers into Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Disputes between States are decided by</t>
+          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Lok Sabha</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Rajya Sabha</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>State Assemblies</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Under Article 131.</t>
+          <t>By 2/3rd majority, under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The power to reorganize the states in India lies with</t>
+          <t>Agriculture is under which list?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Under Article 3.</t>
+          <t>States have exclusive power on this.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Union-State relations are mentioned in which part?</t>
+          <t>Entry related to education in the Concurrent List is</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Entry 11A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Entry 42</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Part XIII</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>Entry 29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Covers legislative, administrative and financial relations.</t>
+          <t>Post-42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Union can legislate on a State subject if</t>
+          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>President gives consent</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Supreme Court orders</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Prime Minister directs</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>Subjects like forests, education were shifted.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
+          <t>Labour laws are included in which list?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent Lists.</t>
+          <t>Both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
+          <t>Who decides whether a matter is a residuary subject?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Supreme Court</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Union law prevails in case of conflict.</t>
+          <t>It interprets Constitution.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Union can legislate on matters in the State List during</t>
+          <t>The Constitution distributes legislative powers between Centre and States in</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Normal times</t>
+          <t>Two lists</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Constitutional Emergency</t>
+          <t>Four lists</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>No list</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Under Article 250.</t>
+          <t>Union, State, and Concurrent lists.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Law and order is primarily a responsibility of</t>
+          <t>Residuary powers in India belong to</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>State Government</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Union Government</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>State Government</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Supreme Court</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The State Government gets revenue from</t>
+          <t>Which of the following is *not* a State subject?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Customs</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Corporation Tax</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>State subjects include land and property taxes.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Police and Public Order are primarily under</t>
+          <t>Which entry relates to defense in Union List?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Entry 5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>These are State subjects.</t>
+          <t>It includes armed forces.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
+          <t>The concept of three lists in Indian Constitution was borrowed from</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Advises on coordination and disputes.</t>
+          <t>7th Schedule follows Australian model.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which commission reviews Centre-State relations in India?</t>
+          <t>The power to legislate on a State List subject during an emergency lies with</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Administrative Reforms Commission</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Established under Article 263.</t>
+          <t>During national emergency, Parliament can legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which list contains subjects on which only the Union Government can legislate?</t>
+          <t>Public Health is listed under</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Union List</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Union List</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Residuary List</t>
@@ -3257,742 +3261,738 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>It includes defense, foreign affairs, etc.</t>
+          <t>States are primarily responsible.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
+          <t>If a subject is not in any list, who can make law on it?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Law and order</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Allows both Centre and State to make laws on it.</t>
+          <t>Residuary power lies with Parliament.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which subject is included in the Union List?</t>
+          <t>Which of these is a State subject?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Trade unions</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>Atomic Energy</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on banking.</t>
+          <t>Only States can legislate on agriculture.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Centre can make laws on State List during</t>
+          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>State law prevails</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Normal Times</t>
+          <t>Both become void</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Only with SC permission</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>When State consents</t>
-        </is>
-      </c>
+          <t>Centre law prevails</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Centre law prevails</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>As per Article 250.</t>
+          <t>Unless state law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The subject of 'banking' falls under which list?</t>
+          <t>Concurrent List initially had how many entries?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on it.</t>
+          <t>Now increased slightly.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The residuary powers in the USA are vested in</t>
+          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Federal Government</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Unlike India, where they are with Centre.</t>
+          <t>These are residuary powers.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a Concurrent List subject?</t>
+          <t>Subjects like police, public health, and local government belong to which list?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marriage and Divorce</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Criminal Procedure</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It is a Union List subject.</t>
+          <t>These are under state jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A State law on a Concurrent subject must get President’s assent if</t>
+          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>It is passed unanimously</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>It has national scope</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Article 254</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Otherwise Union law will prevail.</t>
+          <t>Specifies territorial limits of legislative powers.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agriculture is listed under which list?</t>
+          <t>State List initially had how many entries?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Agriculture is a state subject.</t>
+          <t>Some moved to Concurrent List later.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mines and minerals fall under which list?</t>
+          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>But regulation is also under Union in some cases.</t>
+          <t>Defines Union executive powers.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>During a President's Rule, Parliament can legislate on</t>
+          <t>Who governs the relation between Centre and States in financial matters?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Union List only</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Concurrent List only</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Only with Governor's consent</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>It recommends tax distribution.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
+          <t>Union Government can legislate on State List during</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Central Law</t>
+          <t>Normal time</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Whichever is better</t>
+          <t>Governor’s consent</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>As per judicial interpretation.</t>
+          <t>Article 250 enables this.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concurrent List is also known as</t>
+          <t>Article 262 deals with disputes relating to</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>State-exclusive list</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Union-exclusive list</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>Forests</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Because both Union and State can legislate.</t>
+          <t>It provides for adjudication of inter-State water disputes.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Waterfalls under which subject in Indian Constitution?</t>
+          <t>During President’s Rule, State List powers are exercised by</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>State Governor</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Not Mentioned</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Irrigation, water supply are State subjects.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which is not a function of the Union Government?</t>
+          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Foreign Affairs</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>State Assembly</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Planning and Economic Development fall under</t>
+          <t>Education was transferred to the Concurrent List by</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>86th Amendment</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Both levels can plan for development.</t>
+          <t>To ensure uniform education policy.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
+          <t>Which is true about Union List?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>State prevails</t>
+          <t>States can legislate</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Both are invalid</t>
+          <t>States and Centre legislate together</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Supreme Court decides</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>As per Article 254.</t>
+          <t>States have no authority.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which subject is not included in the State List?</t>
+          <t>The idea of division of powers between Union and States is based on</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>UK Constitution</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>USA Constitution</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Local Government</t>
+          <t>French Constitution</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>India follows a stronger Centre model.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Concurrent List allows</t>
+          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Only Centre to legislate</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Only States to legislate</t>
+          <t>Entry 10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Neither</t>
+          <t>Entry 1A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>But Centre law prevails on conflict.</t>
+          <t>It includes defense of India and armed forces.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Public health is a subject in which list?</t>
+          <t>Land is a subject in</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4022,417 +4022,417 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>States are responsible for hospitals and sanitation.</t>
+          <t>States legislate on land.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The power to legislate on residuary subjects lies with</t>
+          <t>Which list is also known as List I in the Seventh Schedule?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Both Centre and States</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>As per Article 248.</t>
+          <t>It contains 97 subjects.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
+          <t>Education falls under which list?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Part XII</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Covers Articles 245 to 255.</t>
+          <t>Both Centre and State can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Union List has how many subjects?</t>
+          <t>Inter-State Trade and Commerce is a subject under</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Originally had 97 entries.</t>
+          <t>Only Parliament can regulate it.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Article deals with the relationship between Union and State executive powers?</t>
+          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>It defines executive power of the Union.</t>
+          <t>Unless State law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Water supply, sanitation, and public health are responsibilities of</t>
+          <t>State governments derive power to legislate from</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>They are listed in the State List.</t>
+          <t>As per Article 246.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Forests were moved from State to Concurrent List by</t>
+          <t>Which of the following is a subject under the Union List?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>101st Amendment</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>To ensure national policy.</t>
+          <t>Only the Union can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>How many subjects are currently there in the State List?</t>
+          <t>In Union-State relation, India follows</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Dual Federalism</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Confederalism</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Unitary System</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>After the 42nd Amendment.</t>
+          <t>Centre and States work together.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Concurrent List is found in</t>
+          <t>Which entry in the State List deals with public health and sanitation?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Schedule 6</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Entry 7</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Schedule 8</t>
+          <t>Entry 9</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Schedule 9</t>
+          <t>Entry 8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>It contains subjects both Centre and States legislate on.</t>
+          <t>Covers hospitals, sanitation, etc.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Who prepares the Union Budget?</t>
+          <t>Which body resolves disputes between Centre and States?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Presented in Parliament.</t>
+          <t>As per Article 131.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
+          <t>The Constitution provides for inter-governmental coordination through</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>District Magistrates</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>No need for State consent.</t>
+          <t>They promote cooperation among states and Centre.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Forests and wild animal protection fall under</t>
+          <t>Prisons come under which list?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>Residuary List</t>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Both Centre and State can make laws.</t>
+          <t>Administration of jails is a State function.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_FnResp_ofTheUnionandStates.xlsx
+++ b/Data/IP_FnResp_ofTheUnionandStates.xlsx
@@ -472,1703 +472,1703 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Forests and wild animal protection fall under</t>
+          <t>Concurrent List is also known as</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State-exclusive list</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Union-exclusive list</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Both Centre and State can make laws.</t>
+          <t>Because both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
+          <t>The power to reorganize the states in India lies with</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No need for State consent.</t>
+          <t>Under Article 3.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who prepares the Union Budget?</t>
+          <t>A State law on a Concurrent subject must get President’s assent if</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>It is passed unanimously</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>It has national scope</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Presented in Parliament.</t>
+          <t>Otherwise Union law will prevail.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Concurrent List is found in</t>
+          <t>During President’s Rule, State List powers are exercised by</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schedule 6</t>
+          <t>State Governor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Schedule 8</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Schedule 9</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It contains subjects both Centre and States legislate on.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How many subjects are currently there in the State List?</t>
+          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>After the 42nd Amendment.</t>
+          <t>It divides powers into Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forests were moved from State to Concurrent List by</t>
+          <t>Forests and wild animal protection fall under</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101st Amendment</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>To ensure national policy.</t>
+          <t>Both Centre and State can make laws.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Water supply, sanitation, and public health are responsibilities of</t>
+          <t>Land is a subject in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>They are listed in the State List.</t>
+          <t>States legislate on land.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Article deals with the relationship between Union and State executive powers?</t>
+          <t>State governments derive power to legislate from</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>It defines executive power of the Union.</t>
+          <t>As per Article 246.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Union List has how many subjects?</t>
+          <t>Concurrent List allows</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Only Centre to legislate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Only States to legislate</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Neither</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Originally had 97 entries.</t>
+          <t>But Centre law prevails on conflict.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
+          <t>Waterfalls under which subject in Indian Constitution?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Part XII</t>
+          <t>Not Mentioned</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Covers Articles 245 to 255.</t>
+          <t>Irrigation, water supply are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The power to legislate on residuary subjects lies with</t>
+          <t>Planning and Economic Development fall under</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Both Centre and States</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>As per Article 248.</t>
+          <t>Both levels can plan for development.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Public health is a subject in which list?</t>
+          <t>The State Government gets revenue from</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Customs</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Corporation Tax</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>States are responsible for hospitals and sanitation.</t>
+          <t>State subjects include land and property taxes.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concurrent List allows</t>
+          <t>Which body recommends how taxes are distributed between Centre and States?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Only Centre to legislate</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Only States to legislate</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neither</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>But Centre law prevails on conflict.</t>
+          <t>Constituted every 5 years under Article 280.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which subject is not included in the State List?</t>
+          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Central Law</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Local Government</t>
+          <t>Whichever is better</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>As per judicial interpretation.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
+          <t>Which of the following comes under Union List?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State prevails</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Both are invalid</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Supreme Court decides</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>As per Article 254.</t>
+          <t>States cannot legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Planning and Economic Development fall under</t>
+          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Both levels can plan for development.</t>
+          <t>No need for State consent.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which is not a function of the Union Government?</t>
+          <t>Which entry in the State List deals with public health and sanitation?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Foreign Affairs</t>
+          <t>Entry 7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Entry 9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Entry 8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>Covers hospitals, sanitation, etc.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Waterfalls under which subject in Indian Constitution?</t>
+          <t>Who decides whether a matter is a residuary subject?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Mentioned</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Irrigation, water supply are State subjects.</t>
+          <t>It interprets Constitution.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Concurrent List is also known as</t>
+          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State-exclusive list</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Union-exclusive list</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Because both Union and State can legislate.</t>
+          <t>Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
+          <t>If a subject is not in any list, who can make law on it?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central Law</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Whichever is better</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>As per judicial interpretation.</t>
+          <t>Residuary power lies with Parliament.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>During a President's Rule, Parliament can legislate on</t>
+          <t>Which subject is not included in the State List?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Union List only</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Concurrent List only</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Only with Governor's consent</t>
+          <t>Local Government</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mines and minerals fall under which list?</t>
+          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Yes, if President allows</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>But regulation is also under Union in some cases.</t>
+          <t>Article 250 allows this.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agriculture is listed under which list?</t>
+          <t>The idea of division of powers between Union and States is based on</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>UK Constitution</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>USA Constitution</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>French Constitution</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Agriculture is a state subject.</t>
+          <t>India follows a stronger Centre model.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A State law on a Concurrent subject must get President’s assent if</t>
+          <t>Prisons come under which list?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>It is passed unanimously</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>It has national scope</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Otherwise Union law will prevail.</t>
+          <t>Administration of jails is a State function.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a Concurrent List subject?</t>
+          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Marriage and Divorce</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Criminal Procedure</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>It is a Union List subject.</t>
+          <t>Union law prevails in case of conflict.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The residuary powers in the USA are vested in</t>
+          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Federal Government</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Unlike India, where they are with Centre.</t>
+          <t>Unless State law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The subject of 'banking' falls under which list?</t>
+          <t>Residuary powers in India belong to</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on it.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Centre can make laws on State List during</t>
+          <t>Which list is also known as List I in the Seventh Schedule?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Normal Times</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Only with SC permission</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>When State consents</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>As per Article 250.</t>
+          <t>It contains 97 subjects.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which subject is included in the Union List?</t>
+          <t>Which entry relates to defense in Union List?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trade unions</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Entry 3</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>Entry 5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on banking.</t>
+          <t>It includes armed forces.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
+          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Law and order</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Part XII</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Allows both Centre and State to make laws on it.</t>
+          <t>Covers Articles 245 to 255.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which list contains subjects on which only the Union Government can legislate?</t>
+          <t>Which is true about Union List?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>States can legislate</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>States and Centre legislate together</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>It includes defense, foreign affairs, etc.</t>
+          <t>States have no authority.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which commission reviews Centre-State relations in India?</t>
+          <t>Union Government can legislate on State List during</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Normal time</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Administrative Reforms Commission</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Governor’s consent</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Established under Article 263.</t>
+          <t>Article 250 enables this.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
+          <t>Which list contains matters like adoption, succession, and divorce?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Advises on coordination and disputes.</t>
+          <t>Both Parliament and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Police and Public Order are primarily under</t>
+          <t>Which of the following is *not* a State subject?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>These are State subjects.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The State Government gets revenue from</t>
+          <t>The Union can legislate on matters in the State List during</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Customs</t>
+          <t>Normal times</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>Financial Emergency</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Constitutional Emergency</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Corporation Tax</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>State subjects include land and property taxes.</t>
+          <t>Under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Law and order is primarily a responsibility of</t>
+          <t>Which subject is included in the Union List?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Trade unions</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>Only Parliament can legislate on banking.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Union can legislate on matters in the State List during</t>
+          <t>Subjects like police, public health, and local government belong to which list?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Normal times</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Constitutional Emergency</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Under Article 250.</t>
+          <t>These are under state jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
+          <t>The concept of three lists in Indian Constitution was borrowed from</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Union law prevails in case of conflict.</t>
+          <t>7th Schedule follows Australian model.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
+          <t>Which list contains subjects on which only the Union Government can legislate?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent Lists.</t>
+          <t>It includes defense, foreign affairs, etc.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Union can legislate on a State subject if</t>
+          <t>Which of the following is *not* a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>President gives consent</t>
+          <t>Marriage and Divorce</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Supreme Court orders</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>Criminal Procedure</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Prime Minister directs</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>It is a Union List subject.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Union-State relations are mentioned in which part?</t>
+          <t>Who governs the relation between Centre and States in financial matters?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Part XIII</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Covers legislative, administrative and financial relations.</t>
+          <t>It recommends tax distribution.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The power to reorganize the states in India lies with</t>
+          <t>Article 262 deals with disputes relating to</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Forests</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Under Article 3.</t>
+          <t>It provides for adjudication of inter-State water disputes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Disputes between States are decided by</t>
+          <t>Which body resolves disputes between Centre and States?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>Supreme Court</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2186,607 +2186,607 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Under Article 131.</t>
+          <t>As per Article 131.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
+          <t>Union-State relations are mentioned in which part?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yes, if President allows</t>
+          <t>Part XIII</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Article 250 allows this.</t>
+          <t>Covers legislative, administrative and financial relations.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
+          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6th Schedule</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>It contains Union, State, and Concurrent Lists.</t>
+          <t>By 2/3rd majority, under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which list contains matters like adoption, succession, and divorce?</t>
+          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Both Parliament and State can legislate.</t>
+          <t>Subjects like forests, education were shifted.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Electricity appears in which list of the Constitution?</t>
+          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Entry 1A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Both can legislate.</t>
+          <t>It includes defense of India and armed forces.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Language policy is a matter under</t>
+          <t>Union List has how many subjects?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate.</t>
+          <t>Originally had 97 entries.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Planning is a subject under</t>
+          <t>How many subjects are currently there in the State List?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Both Centre and States can plan.</t>
+          <t>After the 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The term "Federal" is used in the Indian Constitution in</t>
+          <t>Entry related to education in the Concurrent List is</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Preamble</t>
+          <t>Entry 11A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Entry 42</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Entry 29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>India is a quasi-federal state, but the term isn't directly used.</t>
+          <t>Post-42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which of the following comes under Union List?</t>
+          <t>The Concurrent List is found in</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Schedule 6</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Schedule 8</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Schedule 9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>States cannot legislate on it.</t>
+          <t>It contains subjects both Centre and States legislate on.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Concurrent List was borrowed from the Constitution of</t>
+          <t>In Union-State relation, India follows</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Dual Federalism</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Confederalism</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Unitary System</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>India’s federal model draws from several countries.</t>
+          <t>Centre and States work together.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
+          <t>Planning is a subject under</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Can be renewed.</t>
+          <t>Both Centre and States can plan.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Who has exclusive power to make laws on residuary subjects?</t>
+          <t>Forests were moved from State to Concurrent List by</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>State Legislatures</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>101st Amendment</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>To ensure national policy.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What does Article 246 deal with?</t>
+          <t>The Constitution distributes legislative powers between Centre and States in</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dispute Redressal</t>
+          <t>Two lists</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Financial emergency</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>Four lists</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Emergency Provisions</t>
+          <t>No list</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Among Union and State.</t>
+          <t>Union, State, and Concurrent lists.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which body recommends how taxes are distributed between Centre and States?</t>
+          <t>What does Article 246 deal with?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Dispute Redressal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Financial emergency</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Emergency Provisions</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Constituted every 5 years under Article 280.</t>
+          <t>Among Union and State.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
+          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>State prevails</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Both are invalid</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Supreme Court decides</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>It divides powers into Union, State, and Concurrent Lists.</t>
+          <t>As per Article 254.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
+          <t>State List initially had how many entries?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>By 2/3rd majority, under Article 249.</t>
+          <t>Some moved to Concurrent List later.</t>
         </is>
       </c>
     </row>
@@ -2832,1247 +2832,1251 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Entry related to education in the Concurrent List is</t>
+          <t>The term "Federal" is used in the Indian Constitution in</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Entry 11A</t>
+          <t>Preamble</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Entry 42</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Entry 29</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Post-42nd Amendment.</t>
+          <t>India is a quasi-federal state, but the term isn't directly used.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
+          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Subjects like forests, education were shifted.</t>
+          <t>These are residuary powers.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Labour laws are included in which list?</t>
+          <t>Who has exclusive power to make laws on residuary subjects?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State Legislatures</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Both Union and State can legislate.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who decides whether a matter is a residuary subject?</t>
+          <t>Mines and minerals fall under which list?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>It interprets Constitution.</t>
+          <t>But regulation is also under Union in some cases.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Constitution distributes legislative powers between Centre and States in</t>
+          <t>Education falls under which list?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Two lists</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Four lists</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No list</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent lists.</t>
+          <t>Both Centre and State can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Residuary powers in India belong to</t>
+          <t>During a President's Rule, Parliament can legislate on</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Union List only</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List only</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Only with Governor's consent</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a State subject?</t>
+          <t>The residuary powers in the USA are vested in</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Federal Government</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>Unlike India, where they are with Centre.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which entry relates to defense in Union List?</t>
+          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Entry 3</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Entry 5</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>It includes armed forces.</t>
+          <t>Can be renewed.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The concept of three lists in Indian Constitution was borrowed from</t>
+          <t>Agriculture is listed under which list?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7th Schedule follows Australian model.</t>
+          <t>Agriculture is a state subject.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The power to legislate on a State List subject during an emergency lies with</t>
+          <t>Which commission reviews Centre-State relations in India?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Administrative Reforms Commission</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>During national emergency, Parliament can legislate on State List.</t>
+          <t>Established under Article 263.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Public Health is listed under</t>
+          <t>Law and order is primarily a responsibility of</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>States are primarily responsible.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>If a subject is not in any list, who can make law on it?</t>
+          <t>Which Article deals with the relationship between Union and State executive powers?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Residuary power lies with Parliament.</t>
+          <t>It defines executive power of the Union.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of these is a State subject?</t>
+          <t>Centre can make laws on State List during</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Normal Times</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Only with SC permission</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atomic Energy</t>
+          <t>When State consents</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Only States can legislate on agriculture.</t>
+          <t>As per Article 250.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
+          <t>The subject of 'banking' falls under which list?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State law prevails</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Both become void</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>None of these</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Unless state law has President’s assent.</t>
+          <t>Only Parliament can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concurrent List initially had how many entries?</t>
+          <t>Inter-State Trade and Commerce is a subject under</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Now increased slightly.</t>
+          <t>Only Parliament can regulate it.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
+          <t>The Constitution provides for inter-governmental coordination through</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>District Magistrates</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>These are residuary powers.</t>
+          <t>They promote cooperation among states and Centre.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Subjects like police, public health, and local government belong to which list?</t>
+          <t>Which is not a function of the Union Government?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Foreign Affairs</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>These are under state jurisdiction.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
+          <t>Concurrent List was borrowed from the Constitution of</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 254</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Specifies territorial limits of legislative powers.</t>
+          <t>India’s federal model draws from several countries.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>State List initially had how many entries?</t>
+          <t>Language policy is a matter under</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Some moved to Concurrent List later.</t>
+          <t>Both Centre and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
+          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>6th Schedule</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Defines Union executive powers.</t>
+          <t>It contains Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Who governs the relation between Centre and States in financial matters?</t>
+          <t>Concurrent List initially had how many entries?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>It recommends tax distribution.</t>
+          <t>Now increased slightly.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Union Government can legislate on State List during</t>
+          <t>The Union can legislate on a State subject if</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Normal time</t>
+          <t>President gives consent</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Supreme Court orders</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Governor’s consent</t>
+          <t>Prime Minister directs</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Article 250 enables this.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Article 262 deals with disputes relating to</t>
+          <t>Labour laws are included in which list?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forests</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>It provides for adjudication of inter-State water disputes.</t>
+          <t>Both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>During President’s Rule, State List powers are exercised by</t>
+          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Governor</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>Advises on coordination and disputes.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
+          <t>Education was transferred to the Concurrent List by</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>86th Amendment</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>State Assembly</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>To ensure uniform education policy.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Education was transferred to the Concurrent List by</t>
+          <t>Electricity appears in which list of the Constitution?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>86th Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>To ensure uniform education policy.</t>
+          <t>Both can legislate.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which is true about Union List?</t>
+          <t>The power to legislate on a State List subject during an emergency lies with</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>States can legislate</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>States and Centre legislate together</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>States have no authority.</t>
+          <t>During national emergency, Parliament can legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The idea of division of powers between Union and States is based on</t>
+          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UK Constitution</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>USA Constitution</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>French Constitution</t>
+          <t>State Assembly</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>India follows a stronger Centre model.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
+          <t>The power to legislate on residuary subjects lies with</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Entry 10</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Entry 1A</t>
+          <t>Both Centre and States</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>It includes defense of India and armed forces.</t>
+          <t>As per Article 248.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Land is a subject in</t>
+          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>States legislate on land.</t>
+          <t>Defines Union executive powers.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which list is also known as List I in the Seventh Schedule?</t>
+          <t>Which of the following is a subject under the Union List?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>It contains 97 subjects.</t>
+          <t>Only the Union can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Education falls under which list?</t>
+          <t>Police and Public Order are primarily under</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4082,387 +4086,383 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate on it.</t>
+          <t>These are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Inter-State Trade and Commerce is a subject under</t>
+          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Law and order</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Only Parliament can regulate it.</t>
+          <t>Allows both Centre and State to make laws on it.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
+          <t>Disputes between States are decided by</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Unless State law has President’s assent.</t>
+          <t>Under Article 131.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>State governments derive power to legislate from</t>
+          <t>Public Health is listed under</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>As per Article 246.</t>
+          <t>States are primarily responsible.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which of the following is a subject under the Union List?</t>
+          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>State law prevails</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Both become void</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
+          <t>Centre law prevails</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Centre law prevails</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Only the Union can legislate on it.</t>
+          <t>Unless state law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>In Union-State relation, India follows</t>
+          <t>Public health is a subject in which list?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dual Federalism</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Confederalism</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Unitary System</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Centre and States work together.</t>
+          <t>States are responsible for hospitals and sanitation.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which entry in the State List deals with public health and sanitation?</t>
+          <t>Who prepares the Union Budget?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Entry 7</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Entry 9</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Entry 8</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Covers hospitals, sanitation, etc.</t>
+          <t>Presented in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which body resolves disputes between Centre and States?</t>
+          <t>Water supply, sanitation, and public health are responsibilities of</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>State Government</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Finance Commission</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>As per Article 131.</t>
+          <t>They are listed in the State List.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Constitution provides for inter-governmental coordination through</t>
+          <t>Which of these is a State subject?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>District Magistrates</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Atomic Energy</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>They promote cooperation among states and Centre.</t>
+          <t>Only States can legislate on agriculture.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Prisons come under which list?</t>
+          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 254</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Administration of jails is a State function.</t>
+          <t>Specifies territorial limits of legislative powers.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_FnResp_ofTheUnionandStates.xlsx
+++ b/Data/IP_FnResp_ofTheUnionandStates.xlsx
@@ -472,211 +472,211 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Concurrent List is also known as</t>
+          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State-exclusive list</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Union-exclusive list</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Overlap list</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Because both Union and State can legislate.</t>
+          <t>Can be renewed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The power to reorganize the states in India lies with</t>
+          <t>In Union-State relation, India follows</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Dual Federalism</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Confederalism</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Unitary System</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Cooperative Federalism</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Under Article 3.</t>
+          <t>Centre and States work together.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A State law on a Concurrent subject must get President’s assent if</t>
+          <t>Which list contains subjects on which only the Union Government can legislate?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>It is passed unanimously</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>It has national scope</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>It overrides Union law</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Otherwise Union law will prevail.</t>
+          <t>It includes defense, foreign affairs, etc.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>During President’s Rule, State List powers are exercised by</t>
+          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Governor</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>Subjects like forests, education were shifted.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
+          <t>Concurrent List allows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Only Centre to legislate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Only States to legislate</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Neither</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Both to legislate</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>It divides powers into Union, State, and Concurrent Lists.</t>
+          <t>But Centre law prevails on conflict.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forests and wild animal protection fall under</t>
+          <t>Education falls under which list?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -706,177 +706,177 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Both Centre and State can make laws.</t>
+          <t>Both Centre and State can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Land is a subject in</t>
+          <t>Which Article of the Indian Constitution deals with the distribution of powers between the Union and the States?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>States legislate on land.</t>
+          <t>It divides powers into Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>State governments derive power to legislate from</t>
+          <t>The concept of three lists in Indian Constitution was borrowed from</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>State List in Schedule 7</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>As per Article 246.</t>
+          <t>7th Schedule follows Australian model.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concurrent List allows</t>
+          <t>Concurrent List is also known as</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Only Centre to legislate</t>
+          <t>State-exclusive list</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Only States to legislate</t>
+          <t>Union-exclusive list</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neither</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Both to legislate</t>
+          <t>Overlap list</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>But Centre law prevails on conflict.</t>
+          <t>Because both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waterfalls under which subject in Indian Constitution?</t>
+          <t>A State law on a Concurrent subject must get President’s assent if</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>It is passed unanimously</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>It has national scope</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Mentioned</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>It overrides Union law</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Irrigation, water supply are State subjects.</t>
+          <t>Otherwise Union law will prevail.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Planning and Economic Development fall under</t>
+          <t>Prisons come under which list?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,1289 +896,1289 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Both levels can plan for development.</t>
+          <t>Administration of jails is a State function.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The State Government gets revenue from</t>
+          <t>Electricity appears in which list of the Constitution?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Customs</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Excise Duty</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Corporation Tax</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Property Tax</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>State subjects include land and property taxes.</t>
+          <t>Both can legislate.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which body recommends how taxes are distributed between Centre and States?</t>
+          <t>Public Health is listed under</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Constituted every 5 years under Article 280.</t>
+          <t>States are primarily responsible.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
+          <t>Union List has how many subjects?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central Law</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Whichever is better</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>As per judicial interpretation.</t>
+          <t>Originally had 97 entries.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following comes under Union List?</t>
+          <t>Public health is a subject in which list?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>States cannot legislate on it.</t>
+          <t>States are responsible for hospitals and sanitation.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
+          <t>Which of these is a State subject?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Article 249</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Article 250</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Atomic Energy</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Article 253</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>No need for State consent.</t>
+          <t>Only States can legislate on agriculture.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which entry in the State List deals with public health and sanitation?</t>
+          <t>The power to legislate on residuary subjects lies with</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Entry 7</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Entry 9</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entry 8</t>
+          <t>Both Centre and States</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entry 6</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Covers hospitals, sanitation, etc.</t>
+          <t>As per Article 248.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who decides whether a matter is a residuary subject?</t>
+          <t>Police and Public Order are primarily under</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>It interprets Constitution.</t>
+          <t>These are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
+          <t>Which is not a function of the Union Government?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Foreign Affairs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent Lists.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>If a subject is not in any list, who can make law on it?</t>
+          <t>Concurrent List initially had how many entries?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Residuary power lies with Parliament.</t>
+          <t>Now increased slightly.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which subject is not included in the State List?</t>
+          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Local Government</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>Union law prevails in case of conflict.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
+          <t>Forests were moved from State to Concurrent List by</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yes, if President allows</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>101st Amendment</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes, during Emergency</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Article 250 allows this.</t>
+          <t>To ensure national policy.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The idea of division of powers between Union and States is based on</t>
+          <t>Inter-State Trade and Commerce is a subject under</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UK Constitution</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>USA Constitution</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>French Constitution</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Canadian Constitution</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>India follows a stronger Centre model.</t>
+          <t>Only Parliament can regulate it.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prisons come under which list?</t>
+          <t>If a subject is not in any list, who can make law on it?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Administration of jails is a State function.</t>
+          <t>Residuary power lies with Parliament.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who decides on the subject if a conflict arises between Union and State laws on a Concurrent List subject?</t>
+          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Finance Commission</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Supreme Court</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Union law prevails in case of conflict.</t>
+          <t>Advises on coordination and disputes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
+          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>State Law</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Whichever is later</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Union Law</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Unless State law has President’s assent.</t>
+          <t>By 2/3rd majority, under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Residuary powers in India belong to</t>
+          <t>Land is a subject in</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>States legislate on land.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which list is also known as List I in the Seventh Schedule?</t>
+          <t>Which Article enables Parliament to make laws on State subjects for implementing international agreements?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 249</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 250</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 253</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It contains 97 subjects.</t>
+          <t>No need for State consent.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which entry relates to defense in Union List?</t>
+          <t>Which of the following comes under Union List?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Entry 3</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Entry 5</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It includes armed forces.</t>
+          <t>States cannot legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
+          <t>Which subject is included in the Union List?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Trade unions</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Part XII</t>
+          <t>Marriage</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Covers Articles 245 to 255.</t>
+          <t>Only Parliament can legislate on banking.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which is true about Union List?</t>
+          <t>Which of the following is a subject under the Union List?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>States can legislate</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Public Health</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>States and Centre legislate together</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Only Centre can legislate</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>States have no authority.</t>
+          <t>Only the Union can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Union Government can legislate on State List during</t>
+          <t>Planning is a subject under</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Normal time</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>President’s Rule</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Governor’s consent</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Article 250 enables this.</t>
+          <t>Both Centre and States can plan.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which list contains matters like adoption, succession, and divorce?</t>
+          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>States</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Both Parliament and State can legislate.</t>
+          <t>These are residuary powers.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a State subject?</t>
+          <t>The legislative relations between Centre and States are governed by which Part of the Constitution?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Public order</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Part XII</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Post and Telegraph</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>It is a Union subject.</t>
+          <t>Covers Articles 245 to 255.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Union can legislate on matters in the State List during</t>
+          <t>What does Article 246 deal with?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Normal times</t>
+          <t>Dispute Redressal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
+          <t>Financial emergency</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Constitutional Emergency</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Emergency Provisions</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Distribution of legislative powers</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Under Article 250.</t>
+          <t>Among Union and State.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which subject is included in the Union List?</t>
+          <t>In case of conflict between Union and State law on Concurrent subject, which prevails?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trade unions</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prisons</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Union Law</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on banking.</t>
+          <t>Unless State law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Subjects like police, public health, and local government belong to which list?</t>
+          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Entry 10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Entry 1A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>These are under state jurisdiction.</t>
+          <t>It includes defense of India and armed forces.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The concept of three lists in Indian Constitution was borrowed from</t>
+          <t>Which list contains matters like adoption, succession, and divorce?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7th Schedule follows Australian model.</t>
+          <t>Both Parliament and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which list contains subjects on which only the Union Government can legislate?</t>
+          <t>Water supply, sanitation, and public health are responsibilities of</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It includes defense, foreign affairs, etc.</t>
+          <t>They are listed in the State List.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which of the following is *not* a Concurrent List subject?</t>
+          <t>Concurrent List was borrowed from the Constitution of</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marriage and Divorce</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Criminal Procedure</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>It is a Union List subject.</t>
+          <t>India’s federal model draws from several countries.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who governs the relation between Centre and States in financial matters?</t>
+          <t>Labour laws are included in which list?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>It recommends tax distribution.</t>
+          <t>Both Union and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Article 262 deals with disputes relating to</t>
+          <t>Disputes between States are decided by</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Forests</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>It provides for adjudication of inter-State water disputes.</t>
+          <t>Under Article 131.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which body resolves disputes between Centre and States?</t>
+          <t>Who decides whether a matter is a residuary subject?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Supreme Court</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Finance Commission</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Supreme Court</t>
@@ -2186,1537 +2186,1533 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>As per Article 131.</t>
+          <t>It interprets Constitution.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Union-State relations are mentioned in which part?</t>
+          <t>Agriculture is under which list?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Part IX</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Part XIII</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Part X</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Part XI</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Covers legislative, administrative and financial relations.</t>
+          <t>States have exclusive power on this.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>In matters of national importance, Parliament can legislate on State subjects with the approval of</t>
+          <t>Which list is also known as List I in the Seventh Schedule?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>By 2/3rd majority, under Article 249.</t>
+          <t>It contains 97 subjects.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which amendment transferred five subjects from State List to Concurrent List?</t>
+          <t>The Constitution provides for inter-governmental coordination through</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>District Magistrates</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Zonal Councils</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Subjects like forests, education were shifted.</t>
+          <t>They promote cooperation among states and Centre.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which entry in the Union List empowers the Parliament to make laws on defense matters?</t>
+          <t>Can Parliament make laws on State subjects without Rajya Sabha’s consent?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Entry 10</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Entry 2</t>
+          <t>Yes, if President allows</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Entry 1A</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Entry 1</t>
+          <t>Yes, during Emergency</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It includes defense of India and armed forces.</t>
+          <t>Article 250 allows this.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Union List has how many subjects?</t>
+          <t>Which commission reviews Centre-State relations in India?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Administrative Reforms Commission</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Inter-State Council</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Originally had 97 entries.</t>
+          <t>Established under Article 263.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>How many subjects are currently there in the State List?</t>
+          <t>Language policy is a matter under</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>After the 42nd Amendment.</t>
+          <t>Both Centre and State can legislate.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Entry related to education in the Concurrent List is</t>
+          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Entry 11A</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Entry 42</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Law and order</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Entry 29</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Entry 25</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Post-42nd Amendment.</t>
+          <t>Allows both Centre and State to make laws on it.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Concurrent List is found in</t>
+          <t>Who governs the relation between Centre and States in financial matters?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Schedule 6</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schedule 8</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Schedule 9</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>It contains subjects both Centre and States legislate on.</t>
+          <t>It recommends tax distribution.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>In Union-State relation, India follows</t>
+          <t>Which body recommends how taxes are distributed between Centre and States?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dual Federalism</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Confederalism</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Unitary System</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cooperative Federalism</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Centre and States work together.</t>
+          <t>Constituted every 5 years under Article 280.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Planning is a subject under</t>
+          <t>Which subject is not included in the State List?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Local Government</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Both Centre and States can plan.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Forests were moved from State to Concurrent List by</t>
+          <t>During President’s Rule, State List powers are exercised by</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State Governor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>101st Amendment</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>To ensure national policy.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Constitution distributes legislative powers between Centre and States in</t>
+          <t>Centre can make laws on State List during</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Two lists</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>Normal Times</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Four lists</t>
+          <t>Only with SC permission</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No list</t>
+          <t>When State consents</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Three lists</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Union, State, and Concurrent lists.</t>
+          <t>As per Article 250.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What does Article 246 deal with?</t>
+          <t>Education was transferred to the Concurrent List by</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dispute Redressal</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Financial emergency</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>86th Amendment</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Emergency Provisions</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Distribution of legislative powers</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Among Union and State.</t>
+          <t>To ensure uniform education policy.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
+          <t>Which of the following is *not* a State subject?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>State prevails</t>
+          <t>Public order</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Both are invalid</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Supreme Court decides</t>
+          <t>Prisons</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Union prevails</t>
+          <t>Post and Telegraph</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>As per Article 254.</t>
+          <t>It is a Union subject.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>State List initially had how many entries?</t>
+          <t>Union Government can legislate on State List during</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Normal time</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>President’s Rule</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Governor’s consent</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Some moved to Concurrent List later.</t>
+          <t>Article 250 enables this.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agriculture is under which list?</t>
+          <t>The Constitution divides legislative powers between the Union and States in how many lists?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>States have exclusive power on this.</t>
+          <t>Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The term "Federal" is used in the Indian Constitution in</t>
+          <t>In case of conflict between Union and State laws on a Concurrent subject, the law made by</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Preamble</t>
+          <t>State prevails</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Schedule 7</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Both are invalid</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 1</t>
+          <t>Supreme Court decides</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Not used</t>
+          <t>Union prevails</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>India is a quasi-federal state, but the term isn't directly used.</t>
+          <t>As per Article 254.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Power to legislate on any matter not in the State List or Concurrent List lies with</t>
+          <t>The term "Federal" is used in the Indian Constitution in</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Preamble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Not used</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>These are residuary powers.</t>
+          <t>India is a quasi-federal state, but the term isn't directly used.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who has exclusive power to make laws on residuary subjects?</t>
+          <t>Law and order is primarily a responsibility of</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>State Legislatures</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>State Government</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Under Article 248.</t>
+          <t>It is a State subject.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mines and minerals fall under which list?</t>
+          <t>The subject of 'banking' falls under which list?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Union List</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>None of these</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>Union List</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Residuary List</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>State List</t>
-        </is>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>But regulation is also under Union in some cases.</t>
+          <t>Only Parliament can legislate on it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Education falls under which list?</t>
+          <t>Union-State relations are mentioned in which part?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Part IX</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Part XIII</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Part X</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Part XI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate on it.</t>
+          <t>Covers legislative, administrative and financial relations.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>During a President's Rule, Parliament can legislate on</t>
+          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Union List only</t>
+          <t>6th Schedule</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Concurrent List only</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>8th Schedule</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Only with Governor's consent</t>
+          <t>9th Schedule</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>All State subjects</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Under Article 356.</t>
+          <t>It contains Union, State, and Concurrent Lists.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The residuary powers in the USA are vested in</t>
+          <t>If there is inconsistency between Central and State law on a Concurrent subject and both have President's assent, which prevails?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Federal Government</t>
+          <t>Central Law</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>State Law</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Whichever is better</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>State Governments</t>
+          <t>Whichever is later</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Unlike India, where they are with Centre.</t>
+          <t>As per judicial interpretation.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>If Rajya Sabha passes a resolution under Article 249, law made by Parliament is valid for</t>
+          <t>The power to legislate on a State List subject during an emergency lies with</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Can be renewed.</t>
+          <t>During national emergency, Parliament can legislate on State List.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agriculture is listed under which list?</t>
+          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>State Assembly</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Agriculture is a state subject.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which commission reviews Centre-State relations in India?</t>
+          <t>Who has exclusive power to make laws on residuary subjects?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>State Legislatures</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Administrative Reforms Commission</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Established under Article 263.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Law and order is primarily a responsibility of</t>
+          <t>The idea of division of powers between Union and States is based on</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>UK Constitution</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>USA Constitution</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>French Constitution</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>Canadian Constitution</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>India follows a stronger Centre model.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which Article deals with the relationship between Union and State executive powers?</t>
+          <t>The power to reorganize the states in India lies with</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>It defines executive power of the Union.</t>
+          <t>Under Article 3.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Centre can make laws on State List during</t>
+          <t>Which is true about Union List?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>States can legislate</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Normal Times</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Only with SC permission</t>
+          <t>States and Centre legislate together</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>When State consents</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Only Centre can legislate</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>As per Article 250.</t>
+          <t>States have no authority.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The subject of 'banking' falls under which list?</t>
+          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>State law prevails</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Both become void</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>Centre law prevails</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Centre law prevails</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Only Parliament can legislate on it.</t>
+          <t>Unless state law has President’s assent.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Inter-State Trade and Commerce is a subject under</t>
+          <t>The Union can legislate on matters in the State List during</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Normal times</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Financial Emergency</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Constitutional Emergency</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Only Parliament can regulate it.</t>
+          <t>Under Article 250.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Constitution provides for inter-governmental coordination through</t>
+          <t>Which Article deals with the relationship between Union and State executive powers?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>District Magistrates</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Zonal Councils</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>They promote cooperation among states and Centre.</t>
+          <t>It defines executive power of the Union.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is not a function of the Union Government?</t>
+          <t>State List initially had how many entries?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Foreign Affairs</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It is a State subject.</t>
+          <t>Some moved to Concurrent List later.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concurrent List was borrowed from the Constitution of</t>
+          <t>The Union can legislate on a State subject if</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>President gives consent</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Supreme Court orders</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Prime Minister directs</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Rajya Sabha passes a resolution</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>India’s federal model draws from several countries.</t>
+          <t>Under Article 249.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Language policy is a matter under</t>
+          <t>Article 262 deals with disputes relating to</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Forests</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Both Centre and State can legislate.</t>
+          <t>It provides for adjudication of inter-State water disputes.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which schedule of the Constitution deals with division of powers between Union and State?</t>
+          <t>The Constitution distributes legislative powers between Centre and States in</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6th Schedule</t>
+          <t>Two lists</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8th Schedule</t>
+          <t>Four lists</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>9th Schedule</t>
+          <t>No list</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Three lists</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It contains Union, State, and Concurrent Lists.</t>
+          <t>Union, State, and Concurrent lists.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concurrent List initially had how many entries?</t>
+          <t>Residuary powers in India belong to</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>State Government</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>Union Government</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Now increased slightly.</t>
+          <t>Under Article 248.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Union can legislate on a State subject if</t>
+          <t>Mines and minerals fall under which list?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>President gives consent</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Supreme Court orders</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Prime Minister directs</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rajya Sabha passes a resolution</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>But regulation is also under Union in some cases.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Labour laws are included in which list?</t>
+          <t>Planning and Economic Development fall under</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3726,743 +3722,747 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Concurrent List</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>State List</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>None of these</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>Concurrent List</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Residuary List</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Concurrent List</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Both Union and State can legislate.</t>
+          <t>Both levels can plan for development.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which organ ensures Centre-State legislative relations work smoothly?</t>
+          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 248</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Article 252</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Article 254</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Inter-State Council</t>
+          <t>Article 245</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Advises on coordination and disputes.</t>
+          <t>Specifies territorial limits of legislative powers.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Education was transferred to the Concurrent List by</t>
+          <t>Which entry relates to defense in Union List?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Entry 2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>86th Amendment</t>
+          <t>Entry 3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Entry 5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Entry 1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>To ensure uniform education policy.</t>
+          <t>It includes armed forces.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Electricity appears in which list of the Constitution?</t>
+          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Article 73</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Both can legislate.</t>
+          <t>Defines Union executive powers.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The power to legislate on a State List subject during an emergency lies with</t>
+          <t>How many subjects are currently there in the State List?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>During national emergency, Parliament can legislate on State List.</t>
+          <t>After the 42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who can legislate on a State subject in national interest if Rajya Sabha passes resolution?</t>
+          <t>Which entry in the State List deals with public health and sanitation?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Entry 7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Entry 9</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>State Assembly</t>
+          <t>Entry 8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Entry 6</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Under Article 249.</t>
+          <t>Covers hospitals, sanitation, etc.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The power to legislate on residuary subjects lies with</t>
+          <t>The State Government gets revenue from</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>States</t>
+          <t>Customs</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Excise Duty</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Both Centre and States</t>
+          <t>Corporation Tax</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Property Tax</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>As per Article 248.</t>
+          <t>State subjects include land and property taxes.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which Article provides that the executive power of the Union extends to the matters on which Parliament has power to make laws?</t>
+          <t>State governments derive power to legislate from</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Article 73</t>
+          <t>State List in Schedule 7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Defines Union executive powers.</t>
+          <t>As per Article 246.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which of the following is a subject under the Union List?</t>
+          <t>Waterfalls under which subject in Indian Constitution?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Not Mentioned</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Only the Union can legislate on it.</t>
+          <t>Irrigation, water supply are State subjects.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Police and Public Order are primarily under</t>
+          <t>Which body resolves disputes between Centre and States?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>These are State subjects.</t>
+          <t>As per Article 131.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which subject was transferred from State to Concurrent List by 42nd Amendment?</t>
+          <t>Which of the following is *not* a Concurrent List subject?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Marriage and Divorce</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Criminal Procedure</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Law and order</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Allows both Centre and State to make laws on it.</t>
+          <t>It is a Union List subject.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Disputes between States are decided by</t>
+          <t>Subjects like police, public health, and local government belong to which list?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Under Article 131.</t>
+          <t>These are under state jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Public Health is listed under</t>
+          <t>Who prepares the Union Budget?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Residuary List</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Finance Minister</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>States are primarily responsible.</t>
+          <t>Presented in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What happens if a state law on a concurrent subject conflicts with a central law?</t>
+          <t>The Concurrent List is found in</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>State law prevails</t>
+          <t>Schedule 6</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Both become void</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
+          <t>Schedule 8</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Schedule 9</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Centre law prevails</t>
+          <t>Schedule 7</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Unless state law has President’s assent.</t>
+          <t>It contains subjects both Centre and States legislate on.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Public health is a subject in which list?</t>
+          <t>During a President's Rule, Parliament can legislate on</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Union List</t>
+          <t>Union List only</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>Concurrent List only</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Concurrent List</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Only with Governor's consent</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>State List</t>
+          <t>All State subjects</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>States are responsible for hospitals and sanitation.</t>
+          <t>Under Article 356.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Who prepares the Union Budget?</t>
+          <t>Entry related to education in the Concurrent List is</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Entry 11A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Entry 42</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Entry 29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finance Minister</t>
+          <t>Entry 25</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Presented in Parliament.</t>
+          <t>Post-42nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Water supply, sanitation, and public health are responsibilities of</t>
+          <t>The residuary powers in the USA are vested in</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Union Government</t>
+          <t>Federal Government</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>State Government</t>
+          <t>State Governments</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>They are listed in the State List.</t>
+          <t>Unlike India, where they are with Centre.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which of these is a State subject?</t>
+          <t>Forests and wild animal protection fall under</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atomic Energy</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Only States can legislate on agriculture.</t>
+          <t>Both Centre and State can make laws.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the extent of laws made by Parliament and State Legislatures?</t>
+          <t>Agriculture is listed under which list?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>Union List</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Article 248</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Article 252</t>
+          <t>Concurrent List</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Article 254</t>
+          <t>Residuary List</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Article 245</t>
+          <t>State List</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Specifies territorial limits of legislative powers.</t>
+          <t>Agriculture is a state subject.</t>
         </is>
       </c>
     </row>
